--- a/build/PerformanceXtra_Master_Sheet.xlsx
+++ b/build/PerformanceXtra_Master_Sheet.xlsx
@@ -1274,7 +1274,7 @@
     <t>Stillness Breathing</t>
   </si>
   <si>
-    <t>Extra Activities</t>
+    <t>Advanced</t>
   </si>
   <si>
     <t>Set a timer on your phone (or other device) for 8 minutes. Close your eyes and do your best to sit as still as possible.
